--- a/leave_of_absence_forms/008_health_check_absence_form--leave_of_absence_forms.xlsx
+++ b/leave_of_absence_forms/008_health_check_absence_form--leave_of_absence_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>General Fields</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical History (2)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>General (3)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>General 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>medical_history</t>
+          <t>medical_history_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Medical History (3)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Contact Information 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1213,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1462,34 +1462,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>absence_reason_choices</t>
+          <t>leave_type_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>family_member's_illness_or_bereavement</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Family member's illness or bereavement</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>absence_reason_choices</t>
+          <t>leave_type_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bereavement</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bereavement</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>unpaid</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unpaid</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1535,53 +1535,53 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>medical</t>
+          <t>bereavement</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medical</t>
+          <t>Bereavement</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>leave_type_choices</t>
+          <t>follow_up_visit_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>leave_type_choices</t>
+          <t>follow_up_visit_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bereavement</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bereavement</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>follow_up_visit_choices</t>
+          <t>medical_certificate_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1598,7 +1598,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>follow_up_visit_choices</t>
+          <t>medical_certificate_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1607,40 +1607,6 @@
         </is>
       </c>
       <c r="C23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>medical_certificate_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>medical_certificate_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
         <is>
           <t>False</t>
         </is>
